--- a/abs_fpi/abs_fpi_external.xlsx
+++ b/abs_fpi/abs_fpi_external.xlsx
@@ -96,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -146,6 +146,21 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -623,183 +638,183 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="54" t="inlineStr">
         <is>
           <t>abs_fpi_external.xlsx —— 参数填写与代码生成说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="50" t="inlineStr"/>
+      <c r="A2" s="55" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="51" t="inlineStr">
+      <c r="A3" s="56" t="inlineStr">
         <is>
           <t>这个工作簿怎么用</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="50" t="inlineStr">
+      <c r="A4" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  1.  Global Parameter 的 B 列：全局变量取值（所有 Case 共用）。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  2.  Local Parameter 从 E 列起：每个 Case 一列，右拉复制即可增加。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  3.  改完参数后回到命令行执行：</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="52" t="inlineStr">
+      <c r="A7" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">          excel-codegen render -c &lt;配置&gt;.yaml -x abs_fpi_external.xlsx --write-excel</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="inlineStr">
+      <c r="A8" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">      只想导出代码文件就换成 --outdir &lt;目录&gt;；只预览不写回则什么参数都不加。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="inlineStr">
+      <c r="A9" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">      想确认表里的代码是不是已经过期：excel-codegen check -c &lt;配置&gt;.yaml</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="inlineStr"/>
+      <c r="A10" s="55" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="inlineStr">
+      <c r="A11" s="56" t="inlineStr">
         <is>
           <t>★  部分输出表是公式（engine: excel）：改参数后 Excel 打开即重算，不用跑脚本</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   公式只做「占位符替换」；要生成代码文件（--outdir）或做 CI 检查（check）仍需命令行。</t>
+      <c r="A12" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   公式支持占位符替换与行内分支（{% if %}）；要生成代码文件（--outdir）或做 CI 检查（check）仍需命令行。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="inlineStr">
+      <c r="A13" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">   不带 --write-excel 的 render 只预览，不会改变本文件。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="50" t="inlineStr"/>
+      <c r="A14" s="55" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="51" t="inlineStr">
+      <c r="A15" s="56" t="inlineStr">
         <is>
           <t>输出位置</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="53" t="inlineStr">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  genie_ext: Code @ B2 (horizontal)［公式·自动重算］</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="53" t="inlineStr">
+      <c r="A17" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  ext_summary: Summary @ B2 (vertical)［公式·自动重算］</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="50" t="inlineStr">
+      <c r="A18" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  Template（隐藏）：模板原文，只读参考，改它不影响渲染结果。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="50" t="inlineStr"/>
+      <c r="A19" s="55" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="51" t="inlineStr">
+      <c r="A20" s="56" t="inlineStr">
         <is>
           <t>本次生成</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  时间        2026-09-24 17:00:47</t>
+      <c r="A21" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  时间        2026-09-27 15:22:53</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="50" t="inlineStr">
+      <c r="A22" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  输出指纹      6da152cd11b8</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="50" t="inlineStr">
+      <c r="A23" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  参数指纹      4e2df5a42a76</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="50" t="inlineStr">
+      <c r="A24" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  case 数    3</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="50" t="inlineStr">
+      <c r="A25" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  cases     EXT-T20.559-mu90-kf+1, EXT-T15-mu0-kf-1, EXT-T15-mu90-kf+1</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="53" t="inlineStr">
+      <c r="A26" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  命令      python build.py  (abs_fpi_external.yaml)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="50" t="inlineStr"/>
+      <c r="A27" s="55" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="51" t="inlineStr">
+      <c r="A28" s="56" t="inlineStr">
         <is>
           <t>工况一览（来自上一次渲染）</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="53" t="inlineStr">
+      <c r="A29" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  EXT-T20.559-mu90-kf+1, EXT-T15-mu0-kf-1, EXT-T15-mu90-kf+1</t>
         </is>
@@ -4393,7 +4408,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-09-24 17:00:47</t>
+          <t>2026-09-27 15:22:53</t>
         </is>
       </c>
     </row>

--- a/abs_fpi/abs_fpi_external.xlsx
+++ b/abs_fpi/abs_fpi_external.xlsx
@@ -96,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -146,6 +146,36 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -638,183 +668,183 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="54" t="inlineStr">
+      <c r="A1" s="64" t="inlineStr">
         <is>
           <t>abs_fpi_external.xlsx —— 参数填写与代码生成说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="55" t="inlineStr"/>
+      <c r="A2" s="65" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="56" t="inlineStr">
+      <c r="A3" s="66" t="inlineStr">
         <is>
           <t>这个工作簿怎么用</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="55" t="inlineStr">
+      <c r="A4" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">  1.  Global Parameter 的 B 列：全局变量取值（所有 Case 共用）。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="55" t="inlineStr">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">  2.  Local Parameter 从 E 列起：每个 Case 一列，右拉复制即可增加。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="A6" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">  3.  改完参数后回到命令行执行：</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="57" t="inlineStr">
+      <c r="A7" s="67" t="inlineStr">
         <is>
           <t xml:space="preserve">          excel-codegen render -c &lt;配置&gt;.yaml -x abs_fpi_external.xlsx --write-excel</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="55" t="inlineStr">
+      <c r="A8" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">      只想导出代码文件就换成 --outdir &lt;目录&gt;；只预览不写回则什么参数都不加。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="55" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">      想确认表里的代码是不是已经过期：excel-codegen check -c &lt;配置&gt;.yaml</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="55" t="inlineStr"/>
+      <c r="A10" s="65" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="56" t="inlineStr">
+      <c r="A11" s="66" t="inlineStr">
         <is>
           <t>★  部分输出表是公式（engine: excel）：改参数后 Excel 打开即重算，不用跑脚本</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="55" t="inlineStr">
+      <c r="A12" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">   公式支持占位符替换与行内分支（{% if %}）；要生成代码文件（--outdir）或做 CI 检查（check）仍需命令行。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="55" t="inlineStr">
+      <c r="A13" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">   不带 --write-excel 的 render 只预览，不会改变本文件。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="55" t="inlineStr"/>
+      <c r="A14" s="65" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="56" t="inlineStr">
+      <c r="A15" s="66" t="inlineStr">
         <is>
           <t>输出位置</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="58" t="inlineStr">
+      <c r="A16" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  genie_ext: Code @ B2 (horizontal)［公式·自动重算］</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="58" t="inlineStr">
+      <c r="A17" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  ext_summary: Summary @ B2 (vertical)［公式·自动重算］</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="55" t="inlineStr">
+      <c r="A18" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">  Template（隐藏）：模板原文，只读参考，改它不影响渲染结果。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="55" t="inlineStr"/>
+      <c r="A19" s="65" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="56" t="inlineStr">
+      <c r="A20" s="66" t="inlineStr">
         <is>
           <t>本次生成</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  时间        2026-09-27 15:22:53</t>
+      <c r="A21" s="65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  时间        2026-09-27 16:02:21</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="55" t="inlineStr">
+      <c r="A22" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">  输出指纹      6da152cd11b8</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="55" t="inlineStr">
+      <c r="A23" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">  参数指纹      4e2df5a42a76</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="55" t="inlineStr">
+      <c r="A24" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">  case 数    3</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="55" t="inlineStr">
+      <c r="A25" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">  cases     EXT-T20.559-mu90-kf+1, EXT-T15-mu0-kf-1, EXT-T15-mu90-kf+1</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="58" t="inlineStr">
+      <c r="A26" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  命令      python build.py  (abs_fpi_external.yaml)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="55" t="inlineStr"/>
+      <c r="A27" s="65" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="56" t="inlineStr">
+      <c r="A28" s="66" t="inlineStr">
         <is>
           <t>工况一览（来自上一次渲染）</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="58" t="inlineStr">
+      <c r="A29" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  EXT-T20.559-mu90-kf+1, EXT-T15-mu0-kf-1, EXT-T15-mu90-kf+1</t>
         </is>
@@ -4408,7 +4438,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-09-27 15:22:53</t>
+          <t>2026-09-27 16:02:21</t>
         </is>
       </c>
     </row>
